--- a/data.mn/public/datasets/labor-participation-by-sex.xlsx
+++ b/data.mn/public/datasets/labor-participation-by-sex.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -434,17 +422,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -452,65 +440,65 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1992</v>
+        <v>2009</v>
       </c>
       <c r="B2" t="n">
-        <v>72.7</v>
+        <v>56.5</v>
       </c>
       <c r="C2" t="n">
-        <v>78.90000000000001</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1993</v>
+        <v>2010</v>
       </c>
       <c r="B3" t="n">
-        <v>71.5</v>
+        <v>56.2</v>
       </c>
       <c r="C3" t="n">
-        <v>76.2</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1994</v>
+        <v>2011</v>
       </c>
       <c r="B4" t="n">
-        <v>69.8</v>
+        <v>56.8</v>
       </c>
       <c r="C4" t="n">
-        <v>73.7</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1995</v>
+        <v>2012</v>
       </c>
       <c r="B5" t="n">
-        <v>65.09999999999999</v>
+        <v>58.4</v>
       </c>
       <c r="C5" t="n">
-        <v>71.90000000000001</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1996</v>
+        <v>2013</v>
       </c>
       <c r="B6" t="n">
-        <v>65.59999999999999</v>
+        <v>56.3</v>
       </c>
       <c r="C6" t="n">
-        <v>70.40000000000001</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1997</v>
+        <v>2014</v>
       </c>
       <c r="B7" t="n">
-        <v>64.8</v>
+        <v>56.2</v>
       </c>
       <c r="C7" t="n">
         <v>68.59999999999999</v>
@@ -518,298 +506,122 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1998</v>
+        <v>2015</v>
       </c>
       <c r="B8" t="n">
-        <v>64.59999999999999</v>
+        <v>55.4</v>
       </c>
       <c r="C8" t="n">
-        <v>69.40000000000001</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1999</v>
+        <v>2016</v>
       </c>
       <c r="B9" t="n">
-        <v>64.09999999999999</v>
+        <v>54.2</v>
       </c>
       <c r="C9" t="n">
-        <v>69.3</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2000</v>
+        <v>2017</v>
       </c>
       <c r="B10" t="n">
-        <v>61</v>
+        <v>55.2</v>
       </c>
       <c r="C10" t="n">
-        <v>64.8</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2001</v>
+        <v>2018</v>
       </c>
       <c r="B11" t="n">
-        <v>59.7</v>
+        <v>53.4</v>
       </c>
       <c r="C11" t="n">
-        <v>64.90000000000001</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2002</v>
+        <v>2019</v>
       </c>
       <c r="B12" t="n">
-        <v>60.5</v>
+        <v>55.7</v>
       </c>
       <c r="C12" t="n">
-        <v>64.90000000000001</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2003</v>
+        <v>2020</v>
       </c>
       <c r="B13" t="n">
-        <v>62.2</v>
+        <v>54.1</v>
       </c>
       <c r="C13" t="n">
-        <v>66.90000000000001</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2004</v>
+        <v>2021</v>
       </c>
       <c r="B14" t="n">
-        <v>63.7</v>
+        <v>51.8</v>
       </c>
       <c r="C14" t="n">
-        <v>65.2</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2005</v>
+        <v>2022</v>
       </c>
       <c r="B15" t="n">
-        <v>62.2</v>
+        <v>53.1</v>
       </c>
       <c r="C15" t="n">
-        <v>64.8</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2006</v>
+        <v>2023</v>
       </c>
       <c r="B16" t="n">
-        <v>64.3</v>
+        <v>51.9</v>
       </c>
       <c r="C16" t="n">
-        <v>64.5</v>
+        <v>67.90000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2007</v>
+        <v>2024</v>
       </c>
       <c r="B17" t="n">
-        <v>63.2</v>
+        <v>53.5</v>
       </c>
       <c r="C17" t="n">
-        <v>65.2</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2008</v>
+        <v>2025</v>
       </c>
       <c r="B18" t="n">
-        <v>62.8</v>
+        <v>52.9</v>
       </c>
       <c r="C18" t="n">
-        <v>64.2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>2009</v>
-      </c>
-      <c r="B19" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="C19" t="n">
-        <v>66.7</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>2010</v>
-      </c>
-      <c r="B20" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="C20" t="n">
-        <v>67.2</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>2011</v>
-      </c>
-      <c r="B21" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="C21" t="n">
-        <v>68.7</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>2012</v>
-      </c>
-      <c r="B22" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="C22" t="n">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B23" t="n">
-        <v>56.3</v>
-      </c>
-      <c r="C23" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>2014</v>
-      </c>
-      <c r="B24" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="C24" t="n">
-        <v>68.59999999999999</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B25" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="C25" t="n">
-        <v>68.09999999999999</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>2016</v>
-      </c>
-      <c r="B26" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="C26" t="n">
-        <v>67.3</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>2017</v>
-      </c>
-      <c r="B27" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="C27" t="n">
-        <v>67.5</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B28" t="n">
-        <v>53.4</v>
-      </c>
-      <c r="C28" t="n">
-        <v>69.5</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B29" t="n">
-        <v>55.7</v>
-      </c>
-      <c r="C29" t="n">
-        <v>70.40000000000001</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>2020</v>
-      </c>
-      <c r="B30" t="n">
-        <v>54.1</v>
-      </c>
-      <c r="C30" t="n">
-        <v>68.7</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B31" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="C31" t="n">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B32" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="C32" t="n">
-        <v>68.09999999999999</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B33" t="n">
-        <v>51.9</v>
-      </c>
-      <c r="C33" t="n">
-        <v>67.90000000000001</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B34" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="C34" t="n">
         <v>69.7</v>
       </c>
     </row>
